--- a/BNtables/BNTable.xlsx
+++ b/BNtables/BNTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangqiqian/Desktop/ST-RTA/BNtables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183D7F32-E495-2E4B-AB69-31AF1E42BA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434BBCEA-4ACA-C54A-B6F6-D7D86A253495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" activeTab="2" xr2:uid="{37465112-FFA5-A943-9908-D2C76DED5922}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{37465112-FFA5-A943-9908-D2C76DED5922}"/>
   </bookViews>
   <sheets>
     <sheet name="肇因依賴於速限和道路類別_市區道路" sheetId="6" r:id="rId1"/>
@@ -352,50 +352,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -762,10 +762,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -782,9 +782,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="13"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="14"/>
       <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
@@ -796,8 +796,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="12" t="s">
         <v>15</v>
       </c>
@@ -812,9 +812,9 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
@@ -826,9 +826,9 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
@@ -840,9 +840,9 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
@@ -854,9 +854,9 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
@@ -868,9 +868,9 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
@@ -882,9 +882,9 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="13"/>
       <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
@@ -896,9 +896,9 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="13"/>
       <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
@@ -910,9 +910,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
@@ -924,9 +924,9 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="13"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
@@ -938,8 +938,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
@@ -954,10 +954,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -974,8 +974,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="12" t="s">
         <v>15</v>
       </c>
@@ -990,9 +990,9 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1004,9 +1004,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="13"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="1" t="s">
         <v>30</v>
       </c>
@@ -1038,10 +1038,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -1058,9 +1058,9 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1072,8 +1072,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="17"/>
+      <c r="B22" s="15" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -1090,9 +1090,9 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1104,9 +1104,9 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="13"/>
       <c r="D24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1118,9 +1118,9 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="13"/>
       <c r="D25" s="2" t="s">
         <v>21</v>
       </c>
@@ -1132,9 +1132,9 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="1" t="s">
         <v>6</v>
       </c>
@@ -1146,9 +1146,9 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="13"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1160,8 +1160,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="12" t="s">
         <v>15</v>
       </c>
@@ -1176,9 +1176,9 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="1" t="s">
         <v>33</v>
       </c>
@@ -1190,9 +1190,9 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1204,9 +1204,9 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="13"/>
       <c r="D31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1218,9 +1218,9 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="13"/>
       <c r="D32" s="1" t="s">
         <v>7</v>
       </c>
@@ -1232,9 +1232,9 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="13"/>
       <c r="D33" s="1" t="s">
         <v>21</v>
       </c>
@@ -1246,9 +1246,9 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="14"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="13"/>
       <c r="D34" s="1" t="s">
         <v>5</v>
       </c>
@@ -1260,9 +1260,9 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="13"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="1" t="s">
         <v>6</v>
       </c>
@@ -1274,8 +1274,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="12" t="s">
         <v>14</v>
       </c>
@@ -1290,9 +1290,9 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="14"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="13"/>
       <c r="D37" s="1" t="s">
         <v>31</v>
       </c>
@@ -1304,9 +1304,9 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="14"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="13"/>
       <c r="D38" s="1" t="s">
         <v>33</v>
       </c>
@@ -1318,9 +1318,9 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="14"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="13"/>
       <c r="D39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1332,9 +1332,9 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="14"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="13"/>
       <c r="D40" s="1" t="s">
         <v>30</v>
       </c>
@@ -1346,9 +1346,9 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="14"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="13"/>
       <c r="D41" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,9 +1360,9 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="13"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="14"/>
       <c r="D42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1374,8 +1374,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="9"/>
-      <c r="B43" s="8" t="s">
+      <c r="A43" s="17"/>
+      <c r="B43" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C43" s="12" t="s">
@@ -1392,9 +1392,9 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="14"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="13"/>
       <c r="D44" s="1" t="s">
         <v>21</v>
       </c>
@@ -1406,9 +1406,9 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="14"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="13"/>
       <c r="D45" s="1" t="s">
         <v>34</v>
       </c>
@@ -1420,9 +1420,9 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="14"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="13"/>
       <c r="D46" s="1" t="s">
         <v>30</v>
       </c>
@@ -1434,9 +1434,9 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="13"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="14"/>
       <c r="D47" s="1" t="s">
         <v>7</v>
       </c>
@@ -1448,8 +1448,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="1" t="s">
         <v>15</v>
       </c>
@@ -1464,8 +1464,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="12" t="s">
         <v>14</v>
       </c>
@@ -1480,9 +1480,9 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="14"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="13"/>
       <c r="D50" s="1" t="s">
         <v>36</v>
       </c>
@@ -1494,9 +1494,9 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="14"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="13"/>
       <c r="D51" s="2" t="s">
         <v>41</v>
       </c>
@@ -1508,9 +1508,9 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="14"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="13"/>
       <c r="D52" s="1" t="s">
         <v>8</v>
       </c>
@@ -1522,9 +1522,9 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="14"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="13"/>
       <c r="D53" s="1" t="s">
         <v>21</v>
       </c>
@@ -1536,9 +1536,9 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="14"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="13"/>
       <c r="D54" s="1" t="s">
         <v>31</v>
       </c>
@@ -1550,9 +1550,9 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="14"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="13"/>
       <c r="D55" s="1" t="s">
         <v>32</v>
       </c>
@@ -1564,9 +1564,9 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="14"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="13"/>
       <c r="D56" s="1" t="s">
         <v>33</v>
       </c>
@@ -1578,9 +1578,9 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="14"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="13"/>
       <c r="D57" s="1" t="s">
         <v>9</v>
       </c>
@@ -1592,9 +1592,9 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="14"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="13"/>
       <c r="D58" s="1" t="s">
         <v>34</v>
       </c>
@@ -1606,9 +1606,9 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="13"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="14"/>
       <c r="D59" s="1" t="s">
         <v>30</v>
       </c>
@@ -1621,6 +1621,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A20:A59"/>
+    <mergeCell ref="B2:B14"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C22:C27"/>
     <mergeCell ref="C43:C47"/>
     <mergeCell ref="C49:C59"/>
     <mergeCell ref="B20:B21"/>
@@ -1628,16 +1638,6 @@
     <mergeCell ref="B43:B59"/>
     <mergeCell ref="C28:C35"/>
     <mergeCell ref="C36:C42"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C13"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="A2:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A20:A59"/>
-    <mergeCell ref="B2:B14"/>
-    <mergeCell ref="B15:B18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B2:C2 C16">
@@ -1736,565 +1736,565 @@
   <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" style="16" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="16"/>
-    <col min="4" max="4" width="43.6640625" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" style="16" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="16"/>
+    <col min="1" max="1" width="15.33203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="9"/>
+    <col min="4" max="4" width="43.6640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="10">
         <v>7.9399999999999998E-2</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="10">
         <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="10">
         <v>8.1500000000000003E-2</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="10">
         <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="18" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="10">
         <v>0.1116</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="10">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="10">
         <v>0.18379999999999999</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="10">
         <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="10">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="10">
         <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="10">
         <v>3.6900000000000002E-2</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="10">
         <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="18" t="s">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="10">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="10">
         <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="18" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="10">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="10">
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="10">
         <v>6.5699999999999995E-2</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="10">
         <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="18" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="10">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="10">
         <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="18" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="10">
         <v>7.51E-2</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="10">
         <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="18" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="10">
         <v>0.10780000000000001</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="10">
         <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="18" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="10">
         <v>0.1148</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="10">
         <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="20"/>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="10">
         <v>0.13239999999999999</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="10">
         <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="17" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="10">
         <v>1.11E-2</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="10">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="18" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="10">
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="10">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="21" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="10">
         <v>1.61E-2</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="10">
         <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="18" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="10">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="10">
         <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="18" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="10">
         <v>1.7100000000000001E-2</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="10">
         <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="18" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="10">
         <v>2.12E-2</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="10">
         <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="18" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="10">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="10">
         <v>372</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="18" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="10">
         <v>4.7300000000000002E-2</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="10">
         <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="18" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="10">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="10">
         <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="18" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="10">
         <v>5.1299999999999998E-2</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="10">
         <v>471</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="18" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="10">
         <v>5.5100000000000003E-2</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="10">
         <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="18" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="10">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="10">
         <v>638</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="18" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="10">
         <v>7.6899999999999996E-2</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="10">
         <v>707</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="18" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="10">
         <v>0.1104</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="10">
         <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="18" t="s">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="10">
         <v>0.1128</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="10">
         <v>1037</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="20"/>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="10">
         <v>0.158</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="10">
         <v>1452</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="17" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="10">
         <v>0.1023</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="10">
         <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="18" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="10">
         <v>0.1221</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="10">
         <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="20"/>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="10">
         <v>0.1221</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="10">
         <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="17" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="10">
         <v>6.5199999999999994E-2</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="10">
         <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="18" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="10">
         <v>8.0299999999999996E-2</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="10">
         <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="18" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="10">
         <v>0.10979999999999999</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="10">
         <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="18" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="10">
         <v>0.1148</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="10">
         <v>183</v>
       </c>
     </row>
@@ -2302,329 +2302,329 @@
       <c r="A39" s="20"/>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="10">
         <v>0.25219999999999998</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="10">
         <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="10">
         <v>0.21</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="10">
         <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="17" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="10">
         <v>7.6200000000000004E-2</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="10">
         <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="18" t="s">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="10">
         <v>9.5399999999999999E-2</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="10">
         <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="18" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="10">
         <v>0.1119</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="10">
         <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
       <c r="C44" s="20"/>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="10">
         <v>0.1411</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="10">
         <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="17" t="s">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="10">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="10">
         <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="18" t="s">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="10">
         <v>3.7600000000000001E-2</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="10">
         <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="18" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="10">
         <v>4.0899999999999999E-2</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="10">
         <v>247</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="18" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="10">
         <v>4.1200000000000001E-2</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="10">
         <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="18" t="s">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="10">
         <v>4.87E-2</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="10">
         <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="18" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="10">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="10">
         <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="18" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="10">
         <v>5.6500000000000002E-2</v>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="10">
         <v>341</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="19"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="18" t="s">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="10">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="10">
         <v>390</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="18" t="s">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="10">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="10">
         <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="18" t="s">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="10">
         <v>0.1022</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="10">
         <v>617</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="18" t="s">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="10">
         <v>0.12670000000000001</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="10">
         <v>765</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="20"/>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="10">
         <v>0.1416</v>
       </c>
-      <c r="F56" s="18">
+      <c r="F56" s="10">
         <v>855</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="17" t="s">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="10">
         <v>0.1229</v>
       </c>
-      <c r="F57" s="18">
+      <c r="F57" s="10">
         <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
       <c r="C58" s="20"/>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="10">
         <v>0.12529999999999999</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F58" s="10">
         <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="20"/>
       <c r="B59" s="20"/>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="10">
         <v>0.27779999999999999</v>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="10">
         <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="10">
         <v>0.14960000000000001</v>
       </c>
-      <c r="F60" s="18">
+      <c r="F60" s="10">
         <v>104</v>
       </c>
     </row>
@@ -2632,18 +2632,26 @@
       <c r="A61" s="20"/>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E61" s="18">
+      <c r="E61" s="10">
         <v>0.34670000000000001</v>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="10">
         <v>241</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A2:A39"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B39"/>
+    <mergeCell ref="C6:C15"/>
+    <mergeCell ref="C16:C31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C35:C39"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:C61"/>
@@ -2652,14 +2660,6 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="C45:C56"/>
     <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A2:A39"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="B6:B39"/>
-    <mergeCell ref="C6:C15"/>
-    <mergeCell ref="C16:C31"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C35:C39"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E1:E39">
@@ -2669,16 +2669,6 @@
         <cfvo type="max"/>
         <color theme="5" tint="0.79998168889431442"/>
         <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F39">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="7" tint="0.79998168889431442"/>
-        <color rgb="FF00B0F0"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2699,6 +2689,16 @@
         <cfvo type="max"/>
         <color theme="5" tint="0.79998168889431442"/>
         <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F39">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="7" tint="0.79998168889431442"/>
+        <color rgb="FF00B0F0"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2731,920 +2731,920 @@
   <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="10.83203125" style="16"/>
-    <col min="4" max="4" width="49.83203125" style="16" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="16"/>
+    <col min="1" max="3" width="10.83203125" style="9"/>
+    <col min="4" max="4" width="49.83203125" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="10">
         <v>8.2699999999999996E-2</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="10">
         <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="10">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="10">
         <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="18" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="10">
         <v>0.1605</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="10">
         <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="10">
         <v>0.20569999999999999</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="10">
         <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="17" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="10">
         <v>0.1351</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="10">
         <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="10">
         <v>0.14360000000000001</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="10">
         <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="20"/>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="10">
         <v>0.3972</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="10">
         <v>794</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="17" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="10">
         <v>7.4700000000000003E-2</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="10">
         <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="10">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="10">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="18" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="10">
         <v>9.4299999999999995E-2</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="10">
         <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="18" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="10">
         <v>0.10150000000000001</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="10">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="10">
         <v>0.12330000000000001</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="10">
         <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="10">
         <v>0.13739999999999999</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="10">
         <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="10">
         <v>3.7600000000000001E-2</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="10">
         <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="18" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="10">
         <v>4.3299999999999998E-2</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="10">
         <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="18" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="10">
         <v>6.9599999999999995E-2</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="10">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="18" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="10">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="10">
         <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="18" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="10">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="10">
         <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="18" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="10">
         <v>8.6499999999999994E-2</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="10">
         <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="18" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="10">
         <v>0.1361</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="10">
         <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="10">
         <v>0.16919999999999999</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="10">
         <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="10">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="10">
         <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="18" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="10">
         <v>2.75E-2</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="10">
         <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="18" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="10">
         <v>3.7199999999999997E-2</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="10">
         <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="18" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="10">
         <v>4.4499999999999998E-2</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="10">
         <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="18" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="10">
         <v>4.53E-2</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="10">
         <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="18" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="10">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="10">
         <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="18" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="10">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="10">
         <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="18" t="s">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="10">
         <v>6.54E-2</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="10">
         <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="18" t="s">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="10">
         <v>6.54E-2</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="10">
         <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="18" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="10">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="10">
         <v>459</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="18" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="10">
         <v>0.1065</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="10">
         <v>515</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="20"/>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="10">
         <v>0.16339999999999999</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="10">
         <v>790</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="17" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="10">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="10">
         <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="18" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="10">
         <v>0.05</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="10">
         <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="18" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="10">
         <v>6.0100000000000001E-2</v>
       </c>
-      <c r="F37" s="18">
+      <c r="F37" s="10">
         <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="18" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="10">
         <v>6.6799999999999998E-2</v>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="10">
         <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="18" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="10">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="10">
         <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="19"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="18" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="10">
         <v>0.1</v>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="10">
         <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="18" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="10">
         <v>0.1168</v>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="10">
         <v>313</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="20"/>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="10">
         <v>0.16600000000000001</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="10">
         <v>445</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="17" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="10">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="10">
         <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="18" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="10">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="10">
         <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="18" t="s">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="10">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="10">
         <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="18" t="s">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="10">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="10">
         <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="18" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="10">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="10">
         <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="19"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="18" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="10">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="10">
         <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="18" t="s">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="10">
         <v>1.14E-2</v>
       </c>
-      <c r="F49" s="18">
+      <c r="F49" s="10">
         <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="19"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="18" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="10">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="10">
         <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="21" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="10">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="10">
         <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="19"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="18" t="s">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="10">
         <v>1.72E-2</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="10">
         <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="18" t="s">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="10">
         <v>1.9099999999999999E-2</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="10">
         <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="18" t="s">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="10">
         <v>2.18E-2</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="10">
         <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="18" t="s">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="10">
         <v>2.24E-2</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="10">
         <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="18" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="10">
         <v>3.8600000000000002E-2</v>
       </c>
-      <c r="F56" s="18">
+      <c r="F56" s="10">
         <v>460</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="18" t="s">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="10">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F57" s="18">
+      <c r="F57" s="10">
         <v>637</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="18" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="10">
         <v>6.2E-2</v>
       </c>
-      <c r="F58" s="18">
+      <c r="F58" s="10">
         <v>738</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="19"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="18" t="s">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="10">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="F59" s="18">
+      <c r="F59" s="10">
         <v>745</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="19"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="18" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="10">
         <v>7.0499999999999993E-2</v>
       </c>
-      <c r="F60" s="18">
+      <c r="F60" s="10">
         <v>840</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="18" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="18">
+      <c r="E61" s="10">
         <v>7.3599999999999999E-2</v>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="10">
         <v>876</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="18" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="10">
         <v>7.8600000000000003E-2</v>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="10">
         <v>936</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="18" t="s">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="10">
         <v>0.1225</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="10">
         <v>1459</v>
       </c>
     </row>
@@ -3652,13 +3652,13 @@
       <c r="A64" s="20"/>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="10">
         <v>0.15509999999999999</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="10">
         <v>1847</v>
       </c>
     </row>
